--- a/financial_advisor_forms/044_financial_client_intake_form--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/044_financial_client_intake_form--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>financial_planner</t>
+          <t>financial_planner_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Financial Planner</t>
+          <t>Financial Planner 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>financial_advisor</t>
+          <t>financial_advisor_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Financial Advisor</t>
+          <t>Financial Advisor 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>financial_institution</t>
+          <t>financial_institution_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Financial Institution</t>
+          <t>Financial Institution 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>other_investments</t>
+          <t>other_investments_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Other Investments</t>
+          <t>Other Investments 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>financial_planner_choices</t>
+          <t>financial_planner_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>financial_planner_choices</t>
+          <t>financial_planner_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>financial_advisor_choices</t>
+          <t>financial_advisor_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>financial_advisor_choices</t>
+          <t>financial_advisor_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>financial_institution_choices</t>
+          <t>financial_institution_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,7 +1602,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>financial_institution_choices</t>
+          <t>financial_institution_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>other_investments_choices</t>
+          <t>other_investments_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>other_investments_choices</t>
+          <t>other_investments_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
